--- a/Excel/Libro de excel - Casos de prueba - Luisa Fernanda Espinal y Jose Manuel Jaramillo    (1) (1).xlsx
+++ b/Excel/Libro de excel - Casos de prueba - Luisa Fernanda Espinal y Jose Manuel Jaramillo    (1) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b12s308\Desktop\cdl\CalculadoraAhorroProgramado\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8640F061-D86B-4193-95CC-20BF57B568FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393F10A6-8BDE-4358-B138-86E7E7E74D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
